--- a/output/yearly_benthic_cover_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_17_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.50037469898636</v>
+        <v>45.6433207410272</v>
       </c>
       <c r="M2" t="n">
-        <v>99.76519789379927</v>
+        <v>98.71398419965266</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10476348496969</v>
+        <v>88.00568550665713</v>
       </c>
       <c r="C3" t="n">
-        <v>45.97286342450985</v>
+        <v>45.94146345137415</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228895663951089</v>
+        <v>2.228665439210433</v>
       </c>
       <c r="E3" t="n">
-        <v>5.735781709158015</v>
+        <v>5.712371511469589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429652213170297</v>
+        <v>0.7428884797368109</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98765571653454</v>
+        <v>33.97780449492768</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17640018058336</v>
+        <v>34.1728700678933</v>
       </c>
       <c r="I3" t="n">
-        <v>6.589532360194222</v>
+        <v>6.528032515064238</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643532633231436</v>
+        <v>4.643052998355069</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8952365150303</v>
+        <v>11.99431449334289</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89538715528371</v>
+        <v>48.82989231156415</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634870948239</v>
+        <v>106.7656702562812</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16450543564757</v>
+        <v>86.97710965896968</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67025308944329</v>
+        <v>42.5398252603049</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183525797987351</v>
+        <v>2.178521863210016</v>
       </c>
       <c r="E4" t="n">
-        <v>6.536166873474774</v>
+        <v>6.492412136909243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445287068660777</v>
+        <v>0.7444405266497399</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29582639081934</v>
+        <v>33.21332518276034</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24832051583957</v>
+        <v>34.24426422588803</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502832732747463</v>
+        <v>5.451392431991434</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653304417912985</v>
+        <v>4.652753291560875</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83549456435245</v>
+        <v>13.02289034103031</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31120978064332</v>
+        <v>44.25595016213523</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81695743443905</v>
+        <v>99.81866576347045</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.96866011579718</v>
+        <v>85.70554291434087</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32848477328989</v>
+        <v>42.11427080267713</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125156939209658</v>
+        <v>2.116122827124069</v>
       </c>
       <c r="E5" t="n">
-        <v>7.127089187305841</v>
+        <v>7.0649290090379</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458548731574918</v>
+        <v>0.7457581583929147</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40577993921171</v>
+        <v>32.26200148405776</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30932416524462</v>
+        <v>34.30487528607407</v>
       </c>
       <c r="I5" t="n">
-        <v>4.593862054433536</v>
+        <v>4.550867659698433</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661592957234324</v>
+        <v>4.660988489955717</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0313398842028</v>
+        <v>14.29445708565912</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48731887770878</v>
+        <v>43.43984454410844</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84714353520148</v>
+        <v>99.84857243244468</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.54819672572313</v>
+        <v>84.18445296867624</v>
       </c>
       <c r="C6" t="n">
-        <v>41.62145394525972</v>
+        <v>41.29978648568391</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055795709413465</v>
+        <v>2.041520072848387</v>
       </c>
       <c r="E6" t="n">
-        <v>7.533474881559267</v>
+        <v>7.448874297213587</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469822819061489</v>
+        <v>0.7468796872681054</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34811464041998</v>
+        <v>31.12462224580822</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36118496768285</v>
+        <v>34.35646561433285</v>
       </c>
       <c r="I6" t="n">
-        <v>3.834004982827988</v>
+        <v>3.798093005779438</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668639261913431</v>
+        <v>4.66799804542566</v>
       </c>
       <c r="K6" t="n">
-        <v>15.45180327427689</v>
+        <v>15.81554703132375</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79913550117356</v>
+        <v>42.75825349244516</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87239272071015</v>
+        <v>99.87358700945282</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.97303794014934</v>
+        <v>82.40581743211729</v>
       </c>
       <c r="C7" t="n">
-        <v>40.64170941978452</v>
+        <v>40.1107736840487</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979234753847342</v>
+        <v>1.954619144651633</v>
       </c>
       <c r="E7" t="n">
-        <v>7.786101893805697</v>
+        <v>7.659988879401081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747942304112031</v>
+        <v>0.7478371287640563</v>
       </c>
       <c r="G7" t="n">
-        <v>30.18066322436868</v>
+        <v>29.79974741410485</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40534598915342</v>
+        <v>34.40050792314658</v>
       </c>
       <c r="I7" t="n">
-        <v>3.199110374161973</v>
+        <v>3.169134887273735</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674639400700194</v>
+        <v>4.673982054775353</v>
       </c>
       <c r="K7" t="n">
-        <v>17.02696205985067</v>
+        <v>17.59418256788272</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22482838195294</v>
+        <v>42.18954116457471</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89349986158811</v>
+        <v>99.89449741650611</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.72988880295887</v>
+        <v>87.38592326068927</v>
       </c>
       <c r="C8" t="n">
-        <v>42.90342887620547</v>
+        <v>42.4297024899106</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983425661988878</v>
+        <v>1.958872269077019</v>
       </c>
       <c r="E8" t="n">
-        <v>9.588303015618809</v>
+        <v>9.50852926749296</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749526026045778</v>
+        <v>0.7494643738298074</v>
       </c>
       <c r="G8" t="n">
-        <v>30.67301955055863</v>
+        <v>30.30516085890586</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47819719810579</v>
+        <v>34.47536119617114</v>
       </c>
       <c r="I8" t="n">
-        <v>5.572879687854886</v>
+        <v>5.704382958776187</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684537662786113</v>
+        <v>4.684152336436298</v>
       </c>
       <c r="K8" t="n">
-        <v>12.27011119704112</v>
+        <v>12.61407673931074</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64108978040182</v>
+        <v>44.76648751939618</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81462985364841</v>
+        <v>99.81026674861752</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.62267876641931</v>
+        <v>85.27421383971557</v>
       </c>
       <c r="C9" t="n">
-        <v>41.66107528543014</v>
+        <v>41.2025927592731</v>
       </c>
       <c r="D9" t="n">
-        <v>1.887903668957632</v>
+        <v>1.863308654957881</v>
       </c>
       <c r="E9" t="n">
-        <v>9.901942293895083</v>
+        <v>9.8384058634861</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508835921001377</v>
+        <v>0.7508596082809347</v>
       </c>
       <c r="G9" t="n">
-        <v>29.19580363271185</v>
+        <v>28.82672311497707</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54064523660633</v>
+        <v>34.53954198092299</v>
       </c>
       <c r="I9" t="n">
-        <v>4.652477891522424</v>
+        <v>4.762502065334751</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693022450625861</v>
+        <v>4.692872551755843</v>
       </c>
       <c r="K9" t="n">
-        <v>14.37732123358069</v>
+        <v>14.72578616028443</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80680126743764</v>
+        <v>43.91316599825426</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84519778644847</v>
+        <v>99.84154491781177</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.29434777709146</v>
+        <v>82.9448917497247</v>
       </c>
       <c r="C10" t="n">
-        <v>40.05437968327054</v>
+        <v>39.61143377189648</v>
       </c>
       <c r="D10" t="n">
-        <v>1.783421870116327</v>
+        <v>1.759022809805312</v>
       </c>
       <c r="E10" t="n">
-        <v>10.00112310300999</v>
+        <v>9.950284269279702</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520504373257821</v>
+        <v>0.752059093770564</v>
       </c>
       <c r="G10" t="n">
-        <v>27.58002729183136</v>
+        <v>27.21334619268051</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59432011698598</v>
+        <v>34.59471831344595</v>
       </c>
       <c r="I10" t="n">
-        <v>3.88308972453589</v>
+        <v>3.975091734676632</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70031523328614</v>
+        <v>4.700369336066027</v>
       </c>
       <c r="K10" t="n">
-        <v>16.70565222290853</v>
+        <v>17.05510825027532</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11073259683421</v>
+        <v>43.20116625379112</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87076450301328</v>
+        <v>99.86770827596291</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.75845230774753</v>
+        <v>80.41934249563336</v>
       </c>
       <c r="C11" t="n">
-        <v>38.12004525023617</v>
+        <v>37.70125918570539</v>
       </c>
       <c r="D11" t="n">
-        <v>1.67076401309544</v>
+        <v>1.647147829036847</v>
       </c>
       <c r="E11" t="n">
-        <v>9.909396529022739</v>
+        <v>9.870294965479275</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530562436249842</v>
+        <v>0.7530931230074672</v>
       </c>
       <c r="G11" t="n">
-        <v>25.8378109248914</v>
+        <v>25.48255989191124</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64058720674927</v>
+        <v>34.64228365834349</v>
       </c>
       <c r="I11" t="n">
-        <v>3.240235867707544</v>
+        <v>3.317131009058355</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706601522656153</v>
+        <v>4.706832018796672</v>
       </c>
       <c r="K11" t="n">
-        <v>19.24154769225247</v>
+        <v>19.58065750436666</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53054345405202</v>
+        <v>42.60766409507583</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89213639654066</v>
+        <v>99.88958078514787</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.17898237378492</v>
+        <v>77.92732287363785</v>
       </c>
       <c r="C12" t="n">
-        <v>36.04159053607579</v>
+        <v>35.72178882758634</v>
       </c>
       <c r="D12" t="n">
-        <v>1.557380117893557</v>
+        <v>1.538027920518575</v>
       </c>
       <c r="E12" t="n">
-        <v>9.687461662259068</v>
+        <v>9.677667746278138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539242278077394</v>
+        <v>0.753984646658949</v>
       </c>
       <c r="G12" t="n">
-        <v>24.08436661845925</v>
+        <v>23.7943965375372</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68051447915601</v>
+        <v>34.68329374631166</v>
       </c>
       <c r="I12" t="n">
-        <v>2.70330884441093</v>
+        <v>2.767548234714911</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712026423798372</v>
+        <v>4.712404041618433</v>
       </c>
       <c r="K12" t="n">
-        <v>21.82101762621506</v>
+        <v>22.07267712636214</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04738528582838</v>
+        <v>42.11339151802213</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90999344811924</v>
+        <v>99.90785747197062</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.61076828628738</v>
+        <v>75.35667369763979</v>
       </c>
       <c r="C13" t="n">
-        <v>33.8903781006458</v>
+        <v>33.57780937426076</v>
       </c>
       <c r="D13" t="n">
-        <v>1.445603937192414</v>
+        <v>1.426552084261265</v>
       </c>
       <c r="E13" t="n">
-        <v>9.368006633222029</v>
+        <v>9.361007310452393</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546737228112509</v>
+        <v>0.7547546218976596</v>
       </c>
       <c r="G13" t="n">
-        <v>22.35578508316994</v>
+        <v>22.06978528901991</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71499124931754</v>
+        <v>34.71871260729234</v>
       </c>
       <c r="I13" t="n">
-        <v>2.254996893003897</v>
+        <v>2.308645397855857</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716710767570319</v>
+        <v>4.717216386860374</v>
       </c>
       <c r="K13" t="n">
-        <v>24.38923171371261</v>
+        <v>24.6433263023602</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64529827329682</v>
+        <v>41.70198798352585</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92490808765524</v>
+        <v>99.9231236601468</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.78246219209296</v>
+        <v>82.58364846450596</v>
       </c>
       <c r="C14" t="n">
-        <v>38.48071402911168</v>
+        <v>38.04244434211907</v>
       </c>
       <c r="D14" t="n">
-        <v>1.447193699455991</v>
+        <v>1.428305946917037</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88673089232627</v>
+        <v>11.844241525332</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555036540081514</v>
+        <v>0.7556825487222192</v>
       </c>
       <c r="G14" t="n">
-        <v>24.43360386607205</v>
+        <v>24.06098528955621</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80640172152348</v>
+        <v>36.72546372685461</v>
       </c>
       <c r="I14" t="n">
-        <v>2.731130521156073</v>
+        <v>3.045953497609999</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721897837550948</v>
+        <v>4.723015929513871</v>
       </c>
       <c r="K14" t="n">
-        <v>17.21753780790703</v>
+        <v>17.41635153549406</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21081048509585</v>
+        <v>44.43979701326441</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90906232211456</v>
+        <v>99.89859289087754</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.81740419881835</v>
+        <v>81.71071767579784</v>
       </c>
       <c r="C15" t="n">
-        <v>37.93272422131844</v>
+        <v>37.63235993751715</v>
       </c>
       <c r="D15" t="n">
-        <v>1.41132182513757</v>
+        <v>1.395554040275439</v>
       </c>
       <c r="E15" t="n">
-        <v>11.97250694157449</v>
+        <v>12.00311452757232</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562062056476653</v>
+        <v>0.75646585403511</v>
       </c>
       <c r="G15" t="n">
-        <v>23.82796333062798</v>
+        <v>23.51623346616261</v>
       </c>
       <c r="H15" t="n">
-        <v>36.84062842279339</v>
+        <v>36.77051254082053</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28248868773935</v>
+        <v>2.540925659212406</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72628878529791</v>
+        <v>4.727911587719439</v>
       </c>
       <c r="K15" t="n">
-        <v>18.18259580118165</v>
+        <v>18.28928232420215</v>
       </c>
       <c r="L15" t="n">
-        <v>43.8086677059378</v>
+        <v>43.99374791890264</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92398772843789</v>
+        <v>99.91539018062194</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.12955569917737</v>
+        <v>79.03809608304971</v>
       </c>
       <c r="C16" t="n">
-        <v>35.59716212108827</v>
+        <v>35.35165263685462</v>
       </c>
       <c r="D16" t="n">
-        <v>1.310430484835324</v>
+        <v>1.295673622947332</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43389336358823</v>
+        <v>11.49726810382357</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568126008550522</v>
+        <v>0.7571419842075913</v>
       </c>
       <c r="G16" t="n">
-        <v>22.12457072783485</v>
+        <v>21.8331662793685</v>
       </c>
       <c r="H16" t="n">
-        <v>36.8701706036772</v>
+        <v>36.80337807315597</v>
       </c>
       <c r="I16" t="n">
-        <v>1.903599163042637</v>
+        <v>2.119330618249306</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730078755344078</v>
+        <v>4.732137401297447</v>
       </c>
       <c r="K16" t="n">
-        <v>20.87044430082265</v>
+        <v>20.96190391695028</v>
       </c>
       <c r="L16" t="n">
-        <v>43.46899111454076</v>
+        <v>43.61586217788363</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93659753645167</v>
+        <v>99.92941873168854</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.82804794986362</v>
+        <v>80.95164998582831</v>
       </c>
       <c r="C17" t="n">
-        <v>36.84129630147974</v>
+        <v>36.72099392582339</v>
       </c>
       <c r="D17" t="n">
-        <v>1.311443106222813</v>
+        <v>1.296812570339993</v>
       </c>
       <c r="E17" t="n">
-        <v>12.20714057541709</v>
+        <v>12.35473368487075</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573974198399698</v>
+        <v>0.7578075413922982</v>
       </c>
       <c r="G17" t="n">
-        <v>22.59378392459792</v>
+        <v>22.34391930782446</v>
       </c>
       <c r="H17" t="n">
-        <v>37.35077830780132</v>
+        <v>37.32729049869169</v>
       </c>
       <c r="I17" t="n">
-        <v>1.873770741984694</v>
+        <v>2.134789249007242</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733733873999813</v>
+        <v>4.736297133701865</v>
       </c>
       <c r="K17" t="n">
-        <v>19.17195205013637</v>
+        <v>19.0483500141717</v>
       </c>
       <c r="L17" t="n">
-        <v>43.924340850939</v>
+        <v>44.15955891552022</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93758920255512</v>
+        <v>99.92890285551532</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.25610458418602</v>
+        <v>78.45433908062752</v>
       </c>
       <c r="C18" t="n">
-        <v>34.55806759678694</v>
+        <v>34.55246070603329</v>
       </c>
       <c r="D18" t="n">
-        <v>1.218852056991856</v>
+        <v>1.207754558643779</v>
       </c>
       <c r="E18" t="n">
-        <v>11.60570612641141</v>
+        <v>11.80300076965014</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579015103241341</v>
+        <v>0.7583807633875893</v>
       </c>
       <c r="G18" t="n">
-        <v>20.99860823626681</v>
+        <v>20.80946084206962</v>
       </c>
       <c r="H18" t="n">
-        <v>37.37563734669938</v>
+        <v>37.35552566760959</v>
       </c>
       <c r="I18" t="n">
-        <v>1.562514867966579</v>
+        <v>1.780336708094356</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73688443952584</v>
+        <v>4.739879771172435</v>
       </c>
       <c r="K18" t="n">
-        <v>21.74389541581399</v>
+        <v>21.54566091937248</v>
       </c>
       <c r="L18" t="n">
-        <v>43.64598780012171</v>
+        <v>43.84257867323292</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94795081272264</v>
+        <v>99.94070029863869</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.18055088679843</v>
+        <v>77.50923020070321</v>
       </c>
       <c r="C19" t="n">
-        <v>33.70561385542361</v>
+        <v>33.8788464509466</v>
       </c>
       <c r="D19" t="n">
-        <v>1.180057430437204</v>
+        <v>1.174674939459685</v>
       </c>
       <c r="E19" t="n">
-        <v>11.45617975331212</v>
+        <v>11.72745959185373</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583333276561135</v>
+        <v>0.7588655515029121</v>
       </c>
       <c r="G19" t="n">
-        <v>20.33024724854866</v>
+        <v>20.239503117501</v>
       </c>
       <c r="H19" t="n">
-        <v>37.39693226138187</v>
+        <v>37.37940485305253</v>
       </c>
       <c r="I19" t="n">
-        <v>1.319217567611747</v>
+        <v>1.486412450440135</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739583297850711</v>
+        <v>4.742909696893202</v>
       </c>
       <c r="K19" t="n">
-        <v>22.81944911320159</v>
+        <v>22.4907697992968</v>
       </c>
       <c r="L19" t="n">
-        <v>43.43098815249902</v>
+        <v>43.58086832037032</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9560511211242</v>
+        <v>99.95048457061372</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.41494796898105</v>
+        <v>74.90968008958214</v>
       </c>
       <c r="C20" t="n">
-        <v>31.14243950430505</v>
+        <v>31.50739926286852</v>
       </c>
       <c r="D20" t="n">
-        <v>1.081593438690173</v>
+        <v>1.083133279703235</v>
       </c>
       <c r="E20" t="n">
-        <v>10.68359105097135</v>
+        <v>11.02010626301923</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587069456659313</v>
+        <v>0.7592840589334863</v>
       </c>
       <c r="G20" t="n">
-        <v>18.63389142241352</v>
+        <v>18.66225170454918</v>
       </c>
       <c r="H20" t="n">
-        <v>37.41535709765799</v>
+        <v>37.4000192539177</v>
       </c>
       <c r="I20" t="n">
-        <v>1.099889603170028</v>
+        <v>1.239360161125024</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741918410412072</v>
+        <v>4.745525368334291</v>
       </c>
       <c r="K20" t="n">
-        <v>25.58505203101894</v>
+        <v>25.09031991041784</v>
       </c>
       <c r="L20" t="n">
-        <v>43.23586353224238</v>
+        <v>43.36099159197918</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96335506756635</v>
+        <v>99.95871076526555</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.75598766837192</v>
+        <v>81.28459990224658</v>
       </c>
       <c r="C21" t="n">
-        <v>35.21145844621888</v>
+        <v>35.48935422852951</v>
       </c>
       <c r="D21" t="n">
-        <v>1.082233133664265</v>
+        <v>1.083913440791229</v>
       </c>
       <c r="E21" t="n">
-        <v>12.83735157896439</v>
+        <v>13.15813063797066</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591556734434768</v>
+        <v>0.7598309573518197</v>
       </c>
       <c r="G21" t="n">
-        <v>20.55354343888219</v>
+        <v>20.51304152507233</v>
       </c>
       <c r="H21" t="n">
-        <v>39.34611717818176</v>
+        <v>39.26430554564325</v>
       </c>
       <c r="I21" t="n">
-        <v>1.432863706214107</v>
+        <v>1.756434311968416</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744722959021732</v>
+        <v>4.748943483448874</v>
       </c>
       <c r="K21" t="n">
-        <v>19.24401233162808</v>
+        <v>18.71540009775343</v>
       </c>
       <c r="L21" t="n">
-        <v>45.49679533022868</v>
+        <v>45.73674000388186</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95226610807563</v>
+        <v>99.94149433016479</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_17_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.6433207410272</v>
+        <v>45.28216568731561</v>
       </c>
       <c r="M2" t="n">
-        <v>98.71398419965266</v>
+        <v>99.41430209378126</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00568550665713</v>
+        <v>88.0437380476737</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94146345137415</v>
+        <v>45.92951517275193</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228665439210433</v>
+        <v>2.228772122378879</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712371511469589</v>
+        <v>5.707744160825766</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428884797368109</v>
+        <v>0.7429240407929598</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97780449492768</v>
+        <v>33.97323593075541</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1728700678933</v>
+        <v>34.17450587647615</v>
       </c>
       <c r="I3" t="n">
-        <v>6.528032515064238</v>
+        <v>6.573280661488544</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643052998355069</v>
+        <v>4.643275254955999</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99431449334289</v>
+        <v>11.95626195232628</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82989231156415</v>
+        <v>48.87828020153722</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7656702562812</v>
+        <v>106.7640573266154</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97710965896968</v>
+        <v>87.07125702558241</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5398252603049</v>
+        <v>42.59315088009068</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178521863210016</v>
+        <v>2.181630261180276</v>
       </c>
       <c r="E4" t="n">
-        <v>6.492412136909243</v>
+        <v>6.501891008793538</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444405266497399</v>
+        <v>0.7444852494768721</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21332518276034</v>
+        <v>33.25465121918533</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24426422588803</v>
+        <v>34.24632147593611</v>
       </c>
       <c r="I4" t="n">
-        <v>5.451392431991434</v>
+        <v>5.489245001779834</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652753291560875</v>
+        <v>4.65303280923045</v>
       </c>
       <c r="K4" t="n">
-        <v>13.02289034103031</v>
+        <v>12.92874297441759</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25595016213523</v>
+        <v>44.29551501600594</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81866576347045</v>
+        <v>99.8174088705142</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.70554291434087</v>
+        <v>85.85172991327153</v>
       </c>
       <c r="C5" t="n">
-        <v>42.11427080267713</v>
+        <v>42.22552576546122</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116122827124069</v>
+        <v>2.121959027279053</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0649290090379</v>
+        <v>7.087805041346945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457581583929147</v>
+        <v>0.7458098630049843</v>
       </c>
       <c r="G5" t="n">
-        <v>32.26200148405776</v>
+        <v>32.34508092832859</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30487528607407</v>
+        <v>34.30725369822927</v>
       </c>
       <c r="I5" t="n">
-        <v>4.550867659698433</v>
+        <v>4.582509711301532</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660988489955717</v>
+        <v>4.661311643781151</v>
       </c>
       <c r="K5" t="n">
-        <v>14.29445708565912</v>
+        <v>14.14827008672846</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43984454410844</v>
+        <v>43.47372511998309</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84857243244468</v>
+        <v>99.84752097217277</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.18445296867624</v>
+        <v>84.36367291718425</v>
       </c>
       <c r="C6" t="n">
-        <v>41.29978648568391</v>
+        <v>41.44905754599749</v>
       </c>
       <c r="D6" t="n">
-        <v>2.041520072848387</v>
+        <v>2.049064524445152</v>
       </c>
       <c r="E6" t="n">
-        <v>7.448874297213587</v>
+        <v>7.481742988857591</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468796872681054</v>
+        <v>0.7469368770167626</v>
       </c>
       <c r="G6" t="n">
-        <v>31.12462224580822</v>
+        <v>31.23394797850149</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35646561433285</v>
+        <v>34.35909634277107</v>
       </c>
       <c r="I6" t="n">
-        <v>3.798093005779438</v>
+        <v>3.824528724237406</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66799804542566</v>
+        <v>4.668355481354766</v>
       </c>
       <c r="K6" t="n">
-        <v>15.81554703132375</v>
+        <v>15.63632708281576</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75825349244516</v>
+        <v>42.7873234347617</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87358700945282</v>
+        <v>99.87270806357495</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.40581743211729</v>
+        <v>82.70750310643167</v>
       </c>
       <c r="C7" t="n">
-        <v>40.1107736840487</v>
+        <v>40.38670710310141</v>
       </c>
       <c r="D7" t="n">
-        <v>1.954619144651633</v>
+        <v>1.968344487787311</v>
       </c>
       <c r="E7" t="n">
-        <v>7.659988879401081</v>
+        <v>7.718877891025768</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478371287640563</v>
+        <v>0.7478975434652362</v>
       </c>
       <c r="G7" t="n">
-        <v>29.79974741410485</v>
+        <v>30.00353019725742</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40050792314658</v>
+        <v>34.40328699940086</v>
       </c>
       <c r="I7" t="n">
-        <v>3.169134887273735</v>
+        <v>3.191206340837374</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673982054775353</v>
+        <v>4.674359646657726</v>
       </c>
       <c r="K7" t="n">
-        <v>17.59418256788272</v>
+        <v>17.29249689356832</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18954116457471</v>
+        <v>42.21455909432368</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89449741650611</v>
+        <v>99.89376309099339</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.38592326068927</v>
+        <v>87.54748429311471</v>
       </c>
       <c r="C8" t="n">
-        <v>42.4297024899106</v>
+        <v>42.62843551995702</v>
       </c>
       <c r="D8" t="n">
-        <v>1.958872269077019</v>
+        <v>1.972590180971862</v>
       </c>
       <c r="E8" t="n">
-        <v>9.50852926749296</v>
+        <v>9.513264522881165</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494643738298074</v>
+        <v>0.7495107486347247</v>
       </c>
       <c r="G8" t="n">
-        <v>30.30516085890586</v>
+        <v>30.48501904249783</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47536119617114</v>
+        <v>34.47749443719733</v>
       </c>
       <c r="I8" t="n">
-        <v>5.704382958776187</v>
+        <v>5.665163181964777</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684152336436298</v>
+        <v>4.684442178967029</v>
       </c>
       <c r="K8" t="n">
-        <v>12.61407673931074</v>
+        <v>12.45251570688528</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76648751939618</v>
+        <v>44.73061644647709</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81026674861752</v>
+        <v>99.81156767331939</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.27421383971557</v>
+        <v>85.37238057061329</v>
       </c>
       <c r="C9" t="n">
-        <v>41.2025927592731</v>
+        <v>41.33210899220148</v>
       </c>
       <c r="D9" t="n">
-        <v>1.863308654957881</v>
+        <v>1.87381640285575</v>
       </c>
       <c r="E9" t="n">
-        <v>9.8384058634861</v>
+        <v>9.825186773224099</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508596082809347</v>
+        <v>0.7508948620060942</v>
       </c>
       <c r="G9" t="n">
-        <v>28.82672311497707</v>
+        <v>28.95853851156179</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53954198092299</v>
+        <v>34.54116365228032</v>
       </c>
       <c r="I9" t="n">
-        <v>4.762502065334751</v>
+        <v>4.729687481147132</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692872551755843</v>
+        <v>4.693092887538089</v>
       </c>
       <c r="K9" t="n">
-        <v>14.72578616028443</v>
+        <v>14.62761942938671</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91316599825426</v>
+        <v>43.88290593446834</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84154491781177</v>
+        <v>99.84263435605654</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.9448917497247</v>
+        <v>83.10285921557357</v>
       </c>
       <c r="C10" t="n">
-        <v>39.61143377189648</v>
+        <v>39.79581623365625</v>
       </c>
       <c r="D10" t="n">
-        <v>1.759022809805312</v>
+        <v>1.772020619518198</v>
       </c>
       <c r="E10" t="n">
-        <v>9.950284269279702</v>
+        <v>9.949370994589353</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752059093770564</v>
+        <v>0.7520838576006444</v>
       </c>
       <c r="G10" t="n">
-        <v>27.21334619268051</v>
+        <v>27.38535497682354</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59471831344595</v>
+        <v>34.59585744962963</v>
       </c>
       <c r="I10" t="n">
-        <v>3.975091734676632</v>
+        <v>3.94764720740818</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700369336066027</v>
+        <v>4.700524110004029</v>
       </c>
       <c r="K10" t="n">
-        <v>17.05510825027532</v>
+        <v>16.89714078442641</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20116625379112</v>
+        <v>43.17566277410769</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86770827596291</v>
+        <v>99.86861979219036</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.41934249563336</v>
+        <v>80.57556263129601</v>
       </c>
       <c r="C11" t="n">
-        <v>37.70125918570539</v>
+        <v>37.8798181986164</v>
       </c>
       <c r="D11" t="n">
-        <v>1.647147829036847</v>
+        <v>1.659761543013015</v>
       </c>
       <c r="E11" t="n">
-        <v>9.870294965479275</v>
+        <v>9.86810104769631</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530931230074672</v>
+        <v>0.7531087781389316</v>
       </c>
       <c r="G11" t="n">
-        <v>25.48255989191124</v>
+        <v>25.65046847177786</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64228365834349</v>
+        <v>34.64300379439084</v>
       </c>
       <c r="I11" t="n">
-        <v>3.317131009058355</v>
+        <v>3.29418913291072</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706832018796672</v>
+        <v>4.706929863368323</v>
       </c>
       <c r="K11" t="n">
-        <v>19.58065750436666</v>
+        <v>19.42443736870399</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60766409507583</v>
+        <v>42.58608756580715</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88958078514787</v>
+        <v>99.89034313312754</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.92732287363785</v>
+        <v>78.03912632743155</v>
       </c>
       <c r="C12" t="n">
-        <v>35.72178882758634</v>
+        <v>35.85252980522147</v>
       </c>
       <c r="D12" t="n">
-        <v>1.538027920518575</v>
+        <v>1.548342300190814</v>
       </c>
       <c r="E12" t="n">
-        <v>9.677667746278138</v>
+        <v>9.66372206523431</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753984646658949</v>
+        <v>0.753992877087071</v>
       </c>
       <c r="G12" t="n">
-        <v>23.7943965375372</v>
+        <v>23.92856101634177</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68329374631166</v>
+        <v>34.68367234600525</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767548234714911</v>
+        <v>2.748380240778128</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712404041618433</v>
+        <v>4.712455481794194</v>
       </c>
       <c r="K12" t="n">
-        <v>22.07267712636214</v>
+        <v>21.96087367256847</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11339151802213</v>
+        <v>42.0950912685181</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90785747197062</v>
+        <v>99.90849474630802</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.35667369763979</v>
+        <v>75.55600057202706</v>
       </c>
       <c r="C13" t="n">
-        <v>33.57780937426076</v>
+        <v>33.79321198133537</v>
       </c>
       <c r="D13" t="n">
-        <v>1.426552084261265</v>
+        <v>1.440387912712178</v>
       </c>
       <c r="E13" t="n">
-        <v>9.361007310452393</v>
+        <v>9.372048200784363</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547546218976596</v>
+        <v>0.754755503150952</v>
       </c>
       <c r="G13" t="n">
-        <v>22.06978528901991</v>
+        <v>22.26020050752793</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71871260729234</v>
+        <v>34.71875314494378</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308645397855857</v>
+        <v>2.292633408214417</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717216386860374</v>
+        <v>4.71722189469345</v>
       </c>
       <c r="K13" t="n">
-        <v>24.6433263023602</v>
+        <v>24.44399942797292</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70198798352585</v>
+        <v>41.68644469511455</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9231236601468</v>
+        <v>99.92365610442283</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.58364846450596</v>
+        <v>82.56881425669478</v>
       </c>
       <c r="C14" t="n">
-        <v>38.04244434211907</v>
+        <v>38.20559370159982</v>
       </c>
       <c r="D14" t="n">
-        <v>1.428305946917037</v>
+        <v>1.442065868793494</v>
       </c>
       <c r="E14" t="n">
-        <v>11.844241525332</v>
+        <v>11.815084895962</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556825487222192</v>
+        <v>0.7556347430940544</v>
       </c>
       <c r="G14" t="n">
-        <v>24.06098528955621</v>
+        <v>24.23731516838265</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72546372685461</v>
+        <v>36.7103811906845</v>
       </c>
       <c r="I14" t="n">
-        <v>3.045953497609999</v>
+        <v>2.885615245440244</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723015929513871</v>
+        <v>4.722717144337841</v>
       </c>
       <c r="K14" t="n">
-        <v>17.41635153549406</v>
+        <v>17.43118574330522</v>
       </c>
       <c r="L14" t="n">
-        <v>44.43979701326441</v>
+        <v>44.26714530152493</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89859289087754</v>
+        <v>99.90392474642996</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.71071767579784</v>
+        <v>81.75793974037211</v>
       </c>
       <c r="C15" t="n">
-        <v>37.63235993751715</v>
+        <v>37.84000605510958</v>
       </c>
       <c r="D15" t="n">
-        <v>1.395554040275439</v>
+        <v>1.412263605808302</v>
       </c>
       <c r="E15" t="n">
-        <v>12.00311452757232</v>
+        <v>11.97208321909005</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75646585403511</v>
+        <v>0.756376298996285</v>
       </c>
       <c r="G15" t="n">
-        <v>23.51623346616261</v>
+        <v>23.73641790957196</v>
       </c>
       <c r="H15" t="n">
-        <v>36.77051254082053</v>
+        <v>36.7464075911298</v>
       </c>
       <c r="I15" t="n">
-        <v>2.540925659212406</v>
+        <v>2.407039247048929</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727911587719439</v>
+        <v>4.727351868726782</v>
       </c>
       <c r="K15" t="n">
-        <v>18.28928232420215</v>
+        <v>18.24206025962788</v>
       </c>
       <c r="L15" t="n">
-        <v>43.99374791890264</v>
+        <v>43.83777770622255</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91539018062194</v>
+        <v>99.91984402096001</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.03809608304971</v>
+        <v>79.26953328684883</v>
       </c>
       <c r="C16" t="n">
-        <v>35.35165263685462</v>
+        <v>35.72304558647791</v>
       </c>
       <c r="D16" t="n">
-        <v>1.295673622947332</v>
+        <v>1.318704206217513</v>
       </c>
       <c r="E16" t="n">
-        <v>11.49726810382357</v>
+        <v>11.51355191150859</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571419842075913</v>
+        <v>0.7570148252438739</v>
       </c>
       <c r="G16" t="n">
-        <v>21.8331662793685</v>
+        <v>22.16393172574471</v>
       </c>
       <c r="H16" t="n">
-        <v>36.80337807315597</v>
+        <v>36.77742858660874</v>
       </c>
       <c r="I16" t="n">
-        <v>2.119330618249306</v>
+        <v>2.007559373751213</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732137401297447</v>
+        <v>4.731342657774213</v>
       </c>
       <c r="K16" t="n">
-        <v>20.96190391695028</v>
+        <v>20.73046671315114</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61586217788363</v>
+        <v>43.47962549906403</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92941873168854</v>
+        <v>99.93313779869308</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.95164998582831</v>
+        <v>80.95295571027495</v>
       </c>
       <c r="C17" t="n">
-        <v>36.72099392582339</v>
+        <v>36.95418379645093</v>
       </c>
       <c r="D17" t="n">
-        <v>1.296812570339993</v>
+        <v>1.319785079702311</v>
       </c>
       <c r="E17" t="n">
-        <v>12.35473368487075</v>
+        <v>12.28985408238478</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578075413922982</v>
+        <v>0.7576353110574073</v>
       </c>
       <c r="G17" t="n">
-        <v>22.34391930782446</v>
+        <v>22.61719875230013</v>
       </c>
       <c r="H17" t="n">
-        <v>37.32729049869169</v>
+        <v>37.24267353907248</v>
       </c>
       <c r="I17" t="n">
-        <v>2.134789249007242</v>
+        <v>1.990588251649029</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736297133701865</v>
+        <v>4.735220694108797</v>
       </c>
       <c r="K17" t="n">
-        <v>19.0483500141717</v>
+        <v>19.04704428972505</v>
       </c>
       <c r="L17" t="n">
-        <v>44.15955891552022</v>
+        <v>43.93247331362846</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92890285551532</v>
+        <v>99.93370139980445</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.45433908062752</v>
+        <v>78.63704232838785</v>
       </c>
       <c r="C18" t="n">
-        <v>34.55246070603329</v>
+        <v>34.94503043406435</v>
       </c>
       <c r="D18" t="n">
-        <v>1.207754558643779</v>
+        <v>1.236283010180647</v>
       </c>
       <c r="E18" t="n">
-        <v>11.80300076965014</v>
+        <v>11.78894696465927</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583807633875893</v>
+        <v>0.7581684218283113</v>
       </c>
       <c r="G18" t="n">
-        <v>20.80946084206962</v>
+        <v>21.18622113962258</v>
       </c>
       <c r="H18" t="n">
-        <v>37.35552566760959</v>
+        <v>37.26887937994496</v>
       </c>
       <c r="I18" t="n">
-        <v>1.780336708094356</v>
+        <v>1.659990775725128</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739879771172435</v>
+        <v>4.738552636426947</v>
       </c>
       <c r="K18" t="n">
-        <v>21.54566091937248</v>
+        <v>21.36295767161215</v>
       </c>
       <c r="L18" t="n">
-        <v>43.84257867323292</v>
+        <v>43.63671777622214</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94070029863869</v>
+        <v>99.94470588189864</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.50923020070321</v>
+        <v>77.73098737213849</v>
       </c>
       <c r="C19" t="n">
-        <v>33.8788464509466</v>
+        <v>34.28589317222458</v>
       </c>
       <c r="D19" t="n">
-        <v>1.174674939459685</v>
+        <v>1.203914425147233</v>
       </c>
       <c r="E19" t="n">
-        <v>11.72745959185373</v>
+        <v>11.71230605204326</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588655515029121</v>
+        <v>0.7586210336059998</v>
       </c>
       <c r="G19" t="n">
-        <v>20.239503117501</v>
+        <v>20.63151967171648</v>
       </c>
       <c r="H19" t="n">
-        <v>37.37940485305253</v>
+        <v>37.29112817488677</v>
       </c>
       <c r="I19" t="n">
-        <v>1.486412450440135</v>
+        <v>1.39211655470124</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742909696893202</v>
+        <v>4.741381460037499</v>
       </c>
       <c r="K19" t="n">
-        <v>22.4907697992968</v>
+        <v>22.26901262786153</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58086832037032</v>
+        <v>43.39871800044478</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95048457061372</v>
+        <v>99.95362380053089</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.90968008958214</v>
+        <v>75.29818710858376</v>
       </c>
       <c r="C20" t="n">
-        <v>31.50739926286852</v>
+        <v>32.06691044044453</v>
       </c>
       <c r="D20" t="n">
-        <v>1.083133279703235</v>
+        <v>1.117183225592544</v>
       </c>
       <c r="E20" t="n">
-        <v>11.02010626301923</v>
+        <v>11.06198867583374</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592840589334863</v>
+        <v>0.7590108288618981</v>
       </c>
       <c r="G20" t="n">
-        <v>18.66225170454918</v>
+        <v>19.14520435528914</v>
       </c>
       <c r="H20" t="n">
-        <v>37.4000192539177</v>
+        <v>37.31028913168304</v>
       </c>
       <c r="I20" t="n">
-        <v>1.239360161125024</v>
+        <v>1.160693210936522</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745525368334291</v>
+        <v>4.743817680386864</v>
       </c>
       <c r="K20" t="n">
-        <v>25.09031991041784</v>
+        <v>24.70181289141625</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36099159197918</v>
+        <v>43.19260676384197</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95871076526555</v>
+        <v>99.96133009570275</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.28459990224658</v>
+        <v>81.10699192507127</v>
       </c>
       <c r="C21" t="n">
-        <v>35.48935422852951</v>
+        <v>35.7284500137988</v>
       </c>
       <c r="D21" t="n">
-        <v>1.083913440791229</v>
+        <v>1.117909575005162</v>
       </c>
       <c r="E21" t="n">
-        <v>13.15813063797066</v>
+        <v>13.02472874665038</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598309573518197</v>
+        <v>0.7595043084067796</v>
       </c>
       <c r="G21" t="n">
-        <v>20.51304152507233</v>
+        <v>20.84953664290076</v>
       </c>
       <c r="H21" t="n">
-        <v>39.26430554564325</v>
+        <v>39.02643165628643</v>
       </c>
       <c r="I21" t="n">
-        <v>1.756434311968416</v>
+        <v>1.58197906827938</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748943483448874</v>
+        <v>4.746901927542374</v>
       </c>
       <c r="K21" t="n">
-        <v>18.71540009775343</v>
+        <v>18.89300807492872</v>
       </c>
       <c r="L21" t="n">
-        <v>45.73674000388186</v>
+        <v>45.32584353811136</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94149433016479</v>
+        <v>99.94730162683888</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_17_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.28216568731561</v>
+        <v>43.74557105124482</v>
       </c>
       <c r="M2" t="n">
-        <v>99.41430209378126</v>
+        <v>96.14580576258416</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0437380476737</v>
+        <v>81.42577090834276</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92951517275193</v>
+        <v>43.18132646389832</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228772122378879</v>
+        <v>2.177686429245464</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707744160825766</v>
+        <v>4.141697431356219</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429240407929598</v>
+        <v>0.7375968709638412</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97323593075541</v>
+        <v>32.75603337323385</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17450587647615</v>
+        <v>33.92945606433669</v>
       </c>
       <c r="I3" t="n">
-        <v>6.573280661488544</v>
+        <v>3.073320295682672</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643275254955999</v>
+        <v>4.609980443524007</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95626195232628</v>
+        <v>18.57422909165724</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87828020153722</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640573266154</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07125702558241</v>
+        <v>88.46315059979207</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59315088009068</v>
+        <v>42.77210205921605</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181630261180276</v>
+        <v>2.183380321460099</v>
       </c>
       <c r="E4" t="n">
-        <v>6.501891008793538</v>
+        <v>6.515910413946567</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444852494768721</v>
+        <v>0.7395254301102446</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25465121918533</v>
+        <v>33.44512005661988</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24632147593611</v>
+        <v>34.01816978507125</v>
       </c>
       <c r="I4" t="n">
-        <v>5.489245001779834</v>
+        <v>6.939010654394988</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65303280923045</v>
+        <v>4.622033938189029</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92874297441759</v>
+        <v>11.53684940020794</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29551501600594</v>
+        <v>45.46035137823034</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8174088705142</v>
+        <v>99.76930283765434</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85172991327153</v>
+        <v>87.19703385747138</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22552576546122</v>
+        <v>42.58157095959322</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121959027279053</v>
+        <v>2.122478234867652</v>
       </c>
       <c r="E5" t="n">
-        <v>7.087805041346945</v>
+        <v>7.300045549470322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458098630049843</v>
+        <v>0.7411637833002863</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34508092832859</v>
+        <v>32.51221909668959</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30725369822927</v>
+        <v>34.09353403181316</v>
       </c>
       <c r="I5" t="n">
-        <v>4.582509711301532</v>
+        <v>5.795319515703583</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661311643781151</v>
+        <v>4.632273645626789</v>
       </c>
       <c r="K5" t="n">
-        <v>14.14827008672846</v>
+        <v>12.8029661425286</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47372511998309</v>
+        <v>44.42271260192277</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84752097217277</v>
+        <v>99.80724970404459</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.36367291718425</v>
+        <v>85.68410589778786</v>
       </c>
       <c r="C6" t="n">
-        <v>41.44905754599749</v>
+        <v>41.96788419293647</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049064524445152</v>
+        <v>2.049754171434524</v>
       </c>
       <c r="E6" t="n">
-        <v>7.481742988857591</v>
+        <v>7.856339184967169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469368770167626</v>
+        <v>0.7425588838612073</v>
       </c>
       <c r="G6" t="n">
-        <v>31.23394797850149</v>
+        <v>31.39822855247709</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35909634277107</v>
+        <v>34.15770865761553</v>
       </c>
       <c r="I6" t="n">
-        <v>3.824528724237406</v>
+        <v>4.838523423299807</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668355481354766</v>
+        <v>4.640993024132545</v>
       </c>
       <c r="K6" t="n">
-        <v>15.63632708281576</v>
+        <v>14.31589410221214</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7873234347617</v>
+        <v>43.55524060719294</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87270806357495</v>
+        <v>99.83901890234155</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.70750310643167</v>
+        <v>83.85936584882633</v>
       </c>
       <c r="C7" t="n">
-        <v>40.38670710310141</v>
+        <v>40.89415788590343</v>
       </c>
       <c r="D7" t="n">
-        <v>1.968344487787311</v>
+        <v>1.962345343225707</v>
       </c>
       <c r="E7" t="n">
-        <v>7.718877891025768</v>
+        <v>8.194412792112308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478975434652362</v>
+        <v>0.7437509113869677</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00353019725742</v>
+        <v>30.05929610689319</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40328699940086</v>
+        <v>34.21254192380051</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191206340837374</v>
+        <v>4.038575575239108</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674359646657726</v>
+        <v>4.648443196168548</v>
       </c>
       <c r="K7" t="n">
-        <v>17.29249689356832</v>
+        <v>16.14063415117367</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21455909432368</v>
+        <v>42.83080453449791</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89376309099339</v>
+        <v>99.86559657157501</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.54748429311471</v>
+        <v>81.87399586137022</v>
       </c>
       <c r="C8" t="n">
-        <v>42.62843551995702</v>
+        <v>39.53534844050084</v>
       </c>
       <c r="D8" t="n">
-        <v>1.972590180971862</v>
+        <v>1.868028615588838</v>
       </c>
       <c r="E8" t="n">
-        <v>9.513264522881165</v>
+        <v>8.362245429155472</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495107486347247</v>
+        <v>0.7447713871876811</v>
       </c>
       <c r="G8" t="n">
-        <v>30.48501904249783</v>
+        <v>28.61454814055944</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47749443719733</v>
+        <v>34.25948381063333</v>
       </c>
       <c r="I8" t="n">
-        <v>5.665163181964777</v>
+        <v>3.370097308322462</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684442178967029</v>
+        <v>4.654821169923006</v>
       </c>
       <c r="K8" t="n">
-        <v>12.45251570688528</v>
+        <v>18.12600413862976</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73061644647709</v>
+        <v>42.22646476600165</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81156767331939</v>
+        <v>99.88781734513226</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.37238057061329</v>
+        <v>79.79204828694756</v>
       </c>
       <c r="C9" t="n">
-        <v>41.33210899220148</v>
+        <v>37.97571506866909</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87381640285575</v>
+        <v>1.769985355185897</v>
       </c>
       <c r="E9" t="n">
-        <v>9.825186773224099</v>
+        <v>8.391972834015625</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508948620060942</v>
+        <v>0.7456461959673432</v>
       </c>
       <c r="G9" t="n">
-        <v>28.95853851156179</v>
+        <v>27.11271697413856</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54116365228032</v>
+        <v>34.29972501449778</v>
       </c>
       <c r="I9" t="n">
-        <v>4.729687481147132</v>
+        <v>2.811713188346457</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693092887538089</v>
+        <v>4.660288724795894</v>
       </c>
       <c r="K9" t="n">
-        <v>14.62761942938671</v>
+        <v>20.20795171305245</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88290593446834</v>
+        <v>41.72271940415838</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84263435605654</v>
+        <v>99.90638618587991</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.10285921557357</v>
+        <v>85.04927837129068</v>
       </c>
       <c r="C10" t="n">
-        <v>39.79581623365625</v>
+        <v>41.58639207439164</v>
       </c>
       <c r="D10" t="n">
-        <v>1.772020619518198</v>
+        <v>1.771973667857222</v>
       </c>
       <c r="E10" t="n">
-        <v>9.949370994589353</v>
+        <v>10.42528850664723</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520838576006444</v>
+        <v>0.7464838174625847</v>
       </c>
       <c r="G10" t="n">
-        <v>27.38535497682354</v>
+        <v>28.68936214709367</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59585744962963</v>
+        <v>35.8844437114025</v>
       </c>
       <c r="I10" t="n">
-        <v>3.94764720740818</v>
+        <v>2.866202661686319</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700524110004029</v>
+        <v>4.665523859141154</v>
       </c>
       <c r="K10" t="n">
-        <v>16.89714078442641</v>
+        <v>14.95072162870932</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17566277410769</v>
+        <v>43.36745341268632</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86861979219036</v>
+        <v>99.90456711578727</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.57556263129601</v>
+        <v>84.53236857005064</v>
       </c>
       <c r="C11" t="n">
-        <v>37.8798181986164</v>
+        <v>41.3930912863127</v>
       </c>
       <c r="D11" t="n">
-        <v>1.659761543013015</v>
+        <v>1.741259917064451</v>
       </c>
       <c r="E11" t="n">
-        <v>9.86810104769631</v>
+        <v>10.70371119197499</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7531087781389316</v>
+        <v>0.7472081754094142</v>
       </c>
       <c r="G11" t="n">
-        <v>25.65046847177786</v>
+        <v>28.24107819691815</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64300379439084</v>
+        <v>35.96825542411869</v>
       </c>
       <c r="I11" t="n">
-        <v>3.29418913291072</v>
+        <v>2.460804568256119</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706929863368323</v>
+        <v>4.670051096308838</v>
       </c>
       <c r="K11" t="n">
-        <v>19.42443736870399</v>
+        <v>15.46763142994935</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58608756580715</v>
+        <v>43.05732998316875</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89034313312754</v>
+        <v>99.9180526994308</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.03912632743155</v>
+        <v>82.34938382731856</v>
       </c>
       <c r="C12" t="n">
-        <v>35.85252980522147</v>
+        <v>39.59205115089271</v>
       </c>
       <c r="D12" t="n">
-        <v>1.548342300190814</v>
+        <v>1.649202648342199</v>
       </c>
       <c r="E12" t="n">
-        <v>9.66372206523431</v>
+        <v>10.47988764984175</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753992877087071</v>
+        <v>0.7478289251243251</v>
       </c>
       <c r="G12" t="n">
-        <v>23.92856101634177</v>
+        <v>26.74802336971994</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68367234600525</v>
+        <v>35.99813636631814</v>
       </c>
       <c r="I12" t="n">
-        <v>2.748380240778128</v>
+        <v>2.052374085945189</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712455481794194</v>
+        <v>4.673930782027031</v>
       </c>
       <c r="K12" t="n">
-        <v>21.96087367256847</v>
+        <v>17.65061617268143</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0950912685181</v>
+        <v>42.68897699397429</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90849474630802</v>
+        <v>99.93164431754843</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.55600057202706</v>
+        <v>83.52397623311057</v>
       </c>
       <c r="C13" t="n">
-        <v>33.79321198133537</v>
+        <v>40.57417823271745</v>
       </c>
       <c r="D13" t="n">
-        <v>1.440387912712178</v>
+        <v>1.650452821141634</v>
       </c>
       <c r="E13" t="n">
-        <v>9.372048200784363</v>
+        <v>11.12109720601048</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754755503150952</v>
+        <v>0.7483958144521835</v>
       </c>
       <c r="G13" t="n">
-        <v>22.26020050752793</v>
+        <v>27.08498951731409</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71875314494378</v>
+        <v>36.34211453252119</v>
       </c>
       <c r="I13" t="n">
-        <v>2.292633408214417</v>
+        <v>1.899452501344859</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71722189469345</v>
+        <v>4.677473840326146</v>
       </c>
       <c r="K13" t="n">
-        <v>24.44399942797292</v>
+        <v>16.47602376688942</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68644469511455</v>
+        <v>42.88653087645616</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92365610442283</v>
+        <v>99.93673287606303</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.56881425669478</v>
+        <v>81.30911414242162</v>
       </c>
       <c r="C14" t="n">
-        <v>38.20559370159982</v>
+        <v>38.65388611563841</v>
       </c>
       <c r="D14" t="n">
-        <v>1.442065868793494</v>
+        <v>1.559747883363911</v>
       </c>
       <c r="E14" t="n">
-        <v>11.815084895962</v>
+        <v>10.77389246484029</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556347430940544</v>
+        <v>0.7488817738313033</v>
       </c>
       <c r="G14" t="n">
-        <v>24.23731516838265</v>
+        <v>25.59646330353301</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7103811906845</v>
+        <v>36.36571272892085</v>
       </c>
       <c r="I14" t="n">
-        <v>2.885615245440244</v>
+        <v>1.583904901486601</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722717144337841</v>
+        <v>4.680511086445645</v>
       </c>
       <c r="K14" t="n">
-        <v>17.43118574330522</v>
+        <v>18.69088585757839</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26714530152493</v>
+        <v>42.60246545730138</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90392474642996</v>
+        <v>99.94723743051819</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.75793974037211</v>
+        <v>80.29488040664127</v>
       </c>
       <c r="C15" t="n">
-        <v>37.84000605510958</v>
+        <v>37.84807375010773</v>
       </c>
       <c r="D15" t="n">
-        <v>1.412263605808302</v>
+        <v>1.517143702426358</v>
       </c>
       <c r="E15" t="n">
-        <v>11.97208321909005</v>
+        <v>10.70563352770135</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756376298996285</v>
+        <v>0.7493033897008246</v>
       </c>
       <c r="G15" t="n">
-        <v>23.73641790957196</v>
+        <v>24.89730136487839</v>
       </c>
       <c r="H15" t="n">
-        <v>36.7464075911298</v>
+        <v>36.38618640330944</v>
       </c>
       <c r="I15" t="n">
-        <v>2.407039247048929</v>
+        <v>1.356165832994758</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727351868726782</v>
+        <v>4.683146185630154</v>
       </c>
       <c r="K15" t="n">
-        <v>18.24206025962788</v>
+        <v>19.70511959335873</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83777770622255</v>
+        <v>42.40162656488299</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91984402096001</v>
+        <v>99.95481990834945</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.26953328684883</v>
+        <v>77.73940094996387</v>
       </c>
       <c r="C16" t="n">
-        <v>35.72304558647791</v>
+        <v>35.50225889372324</v>
       </c>
       <c r="D16" t="n">
-        <v>1.318704206217513</v>
+        <v>1.413382986854536</v>
       </c>
       <c r="E16" t="n">
-        <v>11.51355191150859</v>
+        <v>10.16189994696784</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570148252438739</v>
+        <v>0.7496666662041226</v>
       </c>
       <c r="G16" t="n">
-        <v>22.16393172574471</v>
+        <v>23.19452146255566</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77742858660874</v>
+        <v>36.40382711699982</v>
       </c>
       <c r="I16" t="n">
-        <v>2.007559373751213</v>
+        <v>1.130686106606126</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731342657774213</v>
+        <v>4.685416663775767</v>
       </c>
       <c r="K16" t="n">
-        <v>20.73046671315114</v>
+        <v>22.26059905003613</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47962549906403</v>
+        <v>42.19947078310189</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93313779869308</v>
+        <v>99.96232872686126</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.95295571027495</v>
+        <v>82.99802453551446</v>
       </c>
       <c r="C17" t="n">
-        <v>36.95418379645093</v>
+        <v>38.99915272878695</v>
       </c>
       <c r="D17" t="n">
-        <v>1.319785079702311</v>
+        <v>1.41408229555484</v>
       </c>
       <c r="E17" t="n">
-        <v>12.28985408238478</v>
+        <v>12.0102931639377</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576353110574073</v>
+        <v>0.750037583660241</v>
       </c>
       <c r="G17" t="n">
-        <v>22.61719875230013</v>
+        <v>24.84403555028049</v>
       </c>
       <c r="H17" t="n">
-        <v>37.24267353907248</v>
+        <v>38.05987685886444</v>
       </c>
       <c r="I17" t="n">
-        <v>1.990588251649029</v>
+        <v>1.231964185340228</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735220694108797</v>
+        <v>4.687734897876506</v>
       </c>
       <c r="K17" t="n">
-        <v>19.04704428972505</v>
+        <v>17.00197546448556</v>
       </c>
       <c r="L17" t="n">
-        <v>43.93247331362846</v>
+        <v>43.95782664206611</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93370139980445</v>
+        <v>99.95895483533863</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.63704232838785</v>
+        <v>84.67467289978123</v>
       </c>
       <c r="C18" t="n">
-        <v>34.94503043406435</v>
+        <v>39.74405476482171</v>
       </c>
       <c r="D18" t="n">
-        <v>1.236283010180647</v>
+        <v>1.415259293754784</v>
       </c>
       <c r="E18" t="n">
-        <v>11.78894696465927</v>
+        <v>12.6218935240455</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581684218283113</v>
+        <v>0.7506618704422997</v>
       </c>
       <c r="G18" t="n">
-        <v>21.18622113962258</v>
+        <v>24.98932066959957</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26887937994496</v>
+        <v>38.09155564212463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.659990775725128</v>
+        <v>2.114345209550072</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738552636426947</v>
+        <v>4.691636690264374</v>
       </c>
       <c r="K18" t="n">
-        <v>21.36295767161215</v>
+        <v>15.32532710021877</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63671777622214</v>
+        <v>44.86019857437182</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94470588189864</v>
+        <v>99.92958043941231</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.73098737213849</v>
+        <v>81.77898841115115</v>
       </c>
       <c r="C19" t="n">
-        <v>34.28589317222458</v>
+        <v>37.17510992609404</v>
       </c>
       <c r="D19" t="n">
-        <v>1.203914425147233</v>
+        <v>1.311191617660777</v>
       </c>
       <c r="E19" t="n">
-        <v>11.71230605204326</v>
+        <v>11.98764315747858</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586210336059998</v>
+        <v>0.7512013661954541</v>
       </c>
       <c r="G19" t="n">
-        <v>20.63151967171648</v>
+        <v>23.15179129195906</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29112817488677</v>
+        <v>38.11893179283795</v>
       </c>
       <c r="I19" t="n">
-        <v>1.39211655470124</v>
+        <v>1.763220646297759</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741381460037499</v>
+        <v>4.695008538721588</v>
       </c>
       <c r="K19" t="n">
-        <v>22.26901262786153</v>
+        <v>18.22101158884882</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39871800044478</v>
+        <v>44.54514667368073</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95362380053089</v>
+        <v>99.94126818862361</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.29818710858376</v>
+        <v>78.79111781309234</v>
       </c>
       <c r="C20" t="n">
-        <v>32.06691044044453</v>
+        <v>34.45884859166529</v>
       </c>
       <c r="D20" t="n">
-        <v>1.117183225592544</v>
+        <v>1.204461501736659</v>
       </c>
       <c r="E20" t="n">
-        <v>11.06198867583374</v>
+        <v>11.2569011473464</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590108288618981</v>
+        <v>0.7516686205099998</v>
       </c>
       <c r="G20" t="n">
-        <v>19.14520435528914</v>
+        <v>21.26725104996901</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31028913168304</v>
+        <v>38.1426421269076</v>
       </c>
       <c r="I20" t="n">
-        <v>1.160693210936522</v>
+        <v>1.470264488435164</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743817680386864</v>
+        <v>4.697928878187499</v>
       </c>
       <c r="K20" t="n">
-        <v>24.70181289141625</v>
+        <v>21.20888218690765</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19260676384197</v>
+        <v>44.283290870141</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96133009570275</v>
+        <v>99.95102164871395</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.10699192507127</v>
+        <v>75.86984897928964</v>
       </c>
       <c r="C21" t="n">
-        <v>35.7284500137988</v>
+        <v>31.76321688693091</v>
       </c>
       <c r="D21" t="n">
-        <v>1.117909575005162</v>
+        <v>1.100734415628285</v>
       </c>
       <c r="E21" t="n">
-        <v>13.02472874665038</v>
+        <v>10.49178084313049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595043084067796</v>
+        <v>0.7520734610645716</v>
       </c>
       <c r="G21" t="n">
-        <v>20.84953664290076</v>
+        <v>19.43573549071881</v>
       </c>
       <c r="H21" t="n">
-        <v>39.02643165628643</v>
+        <v>38.1631853396614</v>
       </c>
       <c r="I21" t="n">
-        <v>1.58197906827938</v>
+        <v>1.225880297432495</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746901927542374</v>
+        <v>4.700459131653573</v>
       </c>
       <c r="K21" t="n">
-        <v>18.89300807492872</v>
+        <v>24.13015102071038</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32584353811136</v>
+        <v>44.0657914121244</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94730162683888</v>
+        <v>99.95915931976569</v>
       </c>
     </row>
   </sheetData>
